--- a/Check_các_cuộc_thi/IOE/Lần 2/Thống kê IOE - Lần 2.xlsx
+++ b/Check_các_cuộc_thi/IOE/Lần 2/Thống kê IOE - Lần 2.xlsx
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>13/09/2013</t>
+          <t>Trần Hải Phong</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>18/10/2014</t>
+          <t>Lê Ngọc Hân</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>2014-05-02 00:00:00</t>
+          <t>Đỗ Nguyễn Hà Minh</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>2014-04-09 00:00:00</t>
+          <t>Nguyễn Hoàng Hương Trà</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>26/6/2014</t>
+          <t>Bùi Mai Phương</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>2014-09-09 00:00:00</t>
+          <t>Đỗ Trọng Hoàng</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>16/10/2014</t>
+          <t>Trần Đức Tài</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>30/03/2013</t>
+          <t>Đỗ Tuệ Linh</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>2013-02-02 00:00:00</t>
+          <t>Nguyễn Quang Hải Nam</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>2013-02-08 00:00:00</t>
+          <t>Phan Đức Việt</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>2013-08-05 00:00:00</t>
+          <t>Nguyễn Quỳnh Chi</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>14/08/2013</t>
+          <t>Trần An Như</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>24/10/2013</t>
+          <t>Nguyễn Minh Thư</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>2013-05-09 00:00:00</t>
+          <t>Nguyễn Trần Khánh Dương</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>23/9/2013</t>
+          <t>Trần Lê Khánh An</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>2013-04-06 00:00:00</t>
+          <t>Lê Bảo Minh</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>28/02/2013</t>
+          <t>Nguyễn Nam Phong</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>13/09/2013</t>
+          <t>Trần Hải Phong</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>18/10/2014</t>
+          <t>Lê Ngọc Hân</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>2014-05-02 00:00:00</t>
+          <t>Đỗ Nguyễn Hà Minh</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>2014-04-09 00:00:00</t>
+          <t>Nguyễn Hoàng Hương Trà</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>26/6/2014</t>
+          <t>Bùi Mai Phương</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>2014-09-09 00:00:00</t>
+          <t>Đỗ Trọng Hoàng</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>16/10/2014</t>
+          <t>Trần Đức Tài</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>30/03/2013</t>
+          <t>Đỗ Tuệ Linh</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>2013-02-02 00:00:00</t>
+          <t>Nguyễn Quang Hải Nam</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>2013-02-08 00:00:00</t>
+          <t>Phan Đức Việt</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>2013-08-05 00:00:00</t>
+          <t>Nguyễn Quỳnh Chi</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>14/08/2013</t>
+          <t>Trần An Như</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>24/10/2013</t>
+          <t>Nguyễn Minh Thư</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>2013-05-09 00:00:00</t>
+          <t>Nguyễn Trần Khánh Dương</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>23/9/2013</t>
+          <t>Trần Lê Khánh An</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>2013-04-06 00:00:00</t>
+          <t>Lê Bảo Minh</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>28/02/2013</t>
+          <t>Nguyễn Nam Phong</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
